--- a/Server/NewServer/bin/commonconfig/setting/npc_relation.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/npc_relation.xlsx
@@ -32,7 +32,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认NPC-全友好</t>
+Default NPC: friendly to all</t>
         </r>
       </text>
     </comment>
@@ -58,7 +58,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认玩家帮手-伙伴</t>
+Default player helper: companion</t>
         </r>
       </text>
     </comment>
@@ -84,7 +84,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认怪物-恶魔</t>
+Default monster: demon</t>
         </r>
       </text>
     </comment>
@@ -110,7 +110,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认蓝队</t>
+Default blue team</t>
         </r>
       </text>
     </comment>
@@ -136,7 +136,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认红队</t>
+Default red team</t>
         </r>
       </text>
     </comment>
@@ -162,7 +162,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -173,7 +173,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认黄队</t>
+Default yellow team</t>
         </r>
       </text>
     </comment>
@@ -188,7 +188,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -199,8 +199,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族1
-与玩家敌对</t>
+Sea faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -215,7 +215,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -226,8 +226,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族2
-与玩家敌对</t>
+Sea faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -242,7 +242,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -253,8 +253,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族3
-与玩家友好</t>
+Sea faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -269,7 +269,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -280,8 +280,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠1
-与玩家敌对</t>
+Desert faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -296,7 +296,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -307,8 +307,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠2
-与玩家敌对</t>
+Desert faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -323,7 +323,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -334,8 +334,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠3
-与玩家友好</t>
+Desert faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -350,7 +350,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -361,8 +361,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山1
-与玩家敌对</t>
+Snow Mountain faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -377,7 +377,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -388,8 +388,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山2
-与玩家敌对</t>
+Snow Mountain faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -404,7 +404,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -415,8 +415,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山3
-与玩家友好</t>
+Snow Mountain faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -431,7 +431,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -442,8 +442,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-陷阱势力1
-与任何势力敌对</t>
+Trap faction 1
+Hostile to all factions</t>
         </r>
       </text>
     </comment>
@@ -458,7 +458,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -469,7 +469,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认NPC-全友好</t>
+Default NPC: friendly to all</t>
         </r>
       </text>
     </comment>
@@ -484,7 +484,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -495,7 +495,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认玩家帮手-伙伴</t>
+Default player helper: companion</t>
         </r>
       </text>
     </comment>
@@ -510,7 +510,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -521,7 +521,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认怪物-恶魔</t>
+Default monster: demon</t>
         </r>
       </text>
     </comment>
@@ -536,7 +536,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -547,7 +547,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认蓝队</t>
+Default blue team</t>
         </r>
       </text>
     </comment>
@@ -562,7 +562,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -573,7 +573,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认红队</t>
+Default red team</t>
         </r>
       </text>
     </comment>
@@ -588,7 +588,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -599,7 +599,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-默认黄队</t>
+Default yellow team</t>
         </r>
       </text>
     </comment>
@@ -614,7 +614,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -625,8 +625,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族1
-与玩家敌对</t>
+Sea faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -641,7 +641,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -652,8 +652,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族2
-与玩家敌对</t>
+Sea faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -668,7 +668,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -679,8 +679,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-海族3
-与玩家友好</t>
+Sea faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -706,8 +706,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠1
-与玩家敌对</t>
+Desert faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -722,7 +722,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -733,8 +733,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠2
-与玩家敌对</t>
+Desert faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -749,7 +749,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -760,8 +760,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-沙漠3
-与玩家友好</t>
+Desert faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -776,7 +776,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -787,8 +787,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山1
-与玩家敌对</t>
+Snow Mountain faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -803,7 +803,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -814,8 +814,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山2
-与玩家敌对</t>
+Snow Mountain faction 2
+Hostile to players</t>
         </r>
       </text>
     </comment>
@@ -830,7 +830,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -841,8 +841,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-雪山3
-与玩家友好</t>
+Snow Mountain faction 3
+Friendly to players</t>
         </r>
       </text>
     </comment>
@@ -857,7 +857,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -868,8 +868,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-未知1
-与玩家敌对</t>
+Unknown faction 1
+Hostile to players</t>
         </r>
       </text>
     </comment>
